--- a/output/20260630_delivery_without_active_problems/problem_2_zero_price_direct_full_41_cases_20260630.xlsx
+++ b/output/20260630_delivery_without_active_problems/problem_2_zero_price_direct_full_41_cases_20260630.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Импорт_абонементы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$U$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$V$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U42"/>
+  <dimension ref="A1:V42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,7 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
     <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="31" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -567,6 +568,11 @@
           <t>manager</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>филиал</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -644,6 +650,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -721,6 +732,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -796,6 +812,11 @@
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -873,6 +894,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -948,6 +974,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n"/>
@@ -1023,6 +1054,11 @@
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Васьковская Виктория Петровна</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -1100,6 +1136,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1175,6 +1216,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1252,6 +1298,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1327,6 +1378,11 @@
       <c r="U11" s="2" t="inlineStr">
         <is>
           <t>Мартынова Дарья Дмитриевна</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
         </is>
       </c>
     </row>
@@ -1404,6 +1460,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1479,6 +1540,11 @@
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -1556,6 +1622,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1631,6 +1702,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n"/>
@@ -1706,6 +1782,11 @@
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>Васьковская Виктория Петровна</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -1783,6 +1864,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1858,6 +1944,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1933,6 +2024,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2008,6 +2104,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2083,6 +2184,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2158,6 +2264,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2233,6 +2344,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n"/>
@@ -2308,6 +2424,11 @@
       <c r="U24" s="2" t="inlineStr">
         <is>
           <t>Петрова Полина Владимировна</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
         </is>
       </c>
     </row>
@@ -2385,6 +2506,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n"/>
@@ -2460,6 +2586,11 @@
       <c r="U26" s="2" t="inlineStr">
         <is>
           <t>Седунова Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
         </is>
       </c>
     </row>
@@ -2537,6 +2668,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2612,6 +2748,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2687,6 +2828,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n"/>
@@ -2762,6 +2908,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2837,6 +2988,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2912,6 +3068,11 @@
       <c r="U32" s="2" t="inlineStr">
         <is>
           <t>Фёдорова Надежда Сергеевна</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
         </is>
       </c>
     </row>
@@ -2989,6 +3150,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -3064,6 +3230,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n"/>
@@ -3139,6 +3310,11 @@
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -3216,6 +3392,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -3291,6 +3472,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -3366,6 +3552,11 @@
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -3443,6 +3634,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -3518,6 +3714,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -3593,6 +3794,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -3670,9 +3876,14 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U42"/>
+  <autoFilter ref="A1:V42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>